--- a/Table/TableAsset/TB_WarningWave.xlsx
+++ b/Table/TableAsset/TB_WarningWave.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,27 +474,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_028</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>초반 웨이브</t>
+          <t>[10:00~11:00] Extension 쉬움</t>
         </is>
       </c>
     </row>
@@ -509,27 +509,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_030</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10초 후 추가</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
@@ -544,27 +544,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MON_003</t>
+          <t>MON_035</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20초 후 강화</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
@@ -579,27 +579,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_030</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
         <v>30</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30초 후 가속</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
@@ -614,305 +614,585 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_034</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>45초 후 폭풍</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WW_CH1_2</t>
+          <t>WW_CH1_1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_035</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Stage2 초반</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WW_CH1_2</t>
+          <t>WW_CH1_1</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MON_TRAFFIC</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MON_003</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>70</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10초 후</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WW_CH1_2</t>
+          <t>WW_CH1_1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_030</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20초 후</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WW_CH1_2</t>
+          <t>WW_CH1_1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_035</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35초 후 폭풍</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WW_CH1_3</t>
+          <t>WW_CH1_1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MON_003</t>
+          <t>MON_030</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Stage3 초반</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WW_CH1_3</t>
+          <t>WW_CH1_1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_034</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10초 후</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WW_CH1_3</t>
+          <t>WW_CH1_1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_035</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="n">
         <v>90</v>
       </c>
-      <c r="G13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>20</v>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20초 후</t>
+          <t>신호등 1분마다</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>WW_CH1_1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MON_TRAFFIC</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>신호등 1분마다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MON_002</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Stage2 초반</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MON_003</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>70</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MON_004</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>90</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MON_001</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>35</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>35초 후 폭풍</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>WW_CH1_3</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MON_003</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>70</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Stage3 초반</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MON_004</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MON_001</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>90</v>
+      </c>
+      <c r="G21" t="n">
         <v>4</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>MON_002</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E22" t="n">
         <v>0.4</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F22" t="n">
         <v>100</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G22" t="n">
         <v>5</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H22" t="n">
         <v>30</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>30초 후 최종</t>
         </is>
